--- a/Targets_Financeiros_modelo.xlsx
+++ b/Targets_Financeiros_modelo.xlsx
@@ -55,7 +55,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +72,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF9C4"/>
         <bgColor rgb="00FFF9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -111,6 +117,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -479,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F181"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -488,6 +495,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -521,6 +529,11 @@
           <t>TARGET_UNID</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TARGET_USD</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -541,6 +554,7 @@
       </c>
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
+      <c r="G2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -561,6 +575,7 @@
       </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
+      <c r="G3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -581,6 +596,7 @@
       </c>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
+      <c r="G4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -601,6 +617,7 @@
       </c>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
+      <c r="G5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -621,6 +638,7 @@
       </c>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
+      <c r="G6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -641,6 +659,7 @@
       </c>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
+      <c r="G7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -661,6 +680,7 @@
       </c>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
+      <c r="G8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -681,6 +701,7 @@
       </c>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
+      <c r="G9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -701,6 +722,7 @@
       </c>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
+      <c r="G10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -721,6 +743,7 @@
       </c>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
+      <c r="G11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -741,6 +764,7 @@
       </c>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
+      <c r="G12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -761,6 +785,7 @@
       </c>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
+      <c r="G13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -781,6 +806,7 @@
       </c>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
+      <c r="G14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -801,6 +827,7 @@
       </c>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
+      <c r="G15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -821,6 +848,7 @@
       </c>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
+      <c r="G16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -841,6 +869,7 @@
       </c>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
+      <c r="G17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -861,6 +890,7 @@
       </c>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
+      <c r="G18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -881,6 +911,7 @@
       </c>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
+      <c r="G19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -901,6 +932,7 @@
       </c>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
+      <c r="G20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -921,6 +953,7 @@
       </c>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
+      <c r="G21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -941,6 +974,7 @@
       </c>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
+      <c r="G22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -961,6 +995,7 @@
       </c>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
+      <c r="G23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -981,6 +1016,7 @@
       </c>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
+      <c r="G24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1001,6 +1037,7 @@
       </c>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
+      <c r="G25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1021,6 +1058,7 @@
       </c>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
+      <c r="G26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1041,6 +1079,7 @@
       </c>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
+      <c r="G27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1061,6 +1100,7 @@
       </c>
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="4" t="n"/>
+      <c r="G28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1081,6 +1121,7 @@
       </c>
       <c r="E29" s="4" t="n"/>
       <c r="F29" s="4" t="n"/>
+      <c r="G29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1101,6 +1142,7 @@
       </c>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
+      <c r="G30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1121,6 +1163,7 @@
       </c>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n"/>
+      <c r="G31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1141,6 +1184,7 @@
       </c>
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
+      <c r="G32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1161,6 +1205,7 @@
       </c>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
+      <c r="G33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1181,6 +1226,7 @@
       </c>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
+      <c r="G34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1201,6 +1247,7 @@
       </c>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="4" t="n"/>
+      <c r="G35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1221,6 +1268,7 @@
       </c>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="4" t="n"/>
+      <c r="G36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1241,6 +1289,7 @@
       </c>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="n"/>
+      <c r="G37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1261,6 +1310,7 @@
       </c>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
+      <c r="G38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1281,6 +1331,7 @@
       </c>
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="n"/>
+      <c r="G39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1301,6 +1352,7 @@
       </c>
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="n"/>
+      <c r="G40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1321,6 +1373,7 @@
       </c>
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="n"/>
+      <c r="G41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1341,6 +1394,7 @@
       </c>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
+      <c r="G42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1361,6 +1415,7 @@
       </c>
       <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="n"/>
+      <c r="G43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1381,6 +1436,7 @@
       </c>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
+      <c r="G44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1401,6 +1457,7 @@
       </c>
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
+      <c r="G45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1421,6 +1478,7 @@
       </c>
       <c r="E46" s="4" t="n"/>
       <c r="F46" s="4" t="n"/>
+      <c r="G46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1441,6 +1499,7 @@
       </c>
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
+      <c r="G47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1461,6 +1520,7 @@
       </c>
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="n"/>
+      <c r="G48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1481,6 +1541,7 @@
       </c>
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="4" t="n"/>
+      <c r="G49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1501,6 +1562,7 @@
       </c>
       <c r="E50" s="4" t="n"/>
       <c r="F50" s="4" t="n"/>
+      <c r="G50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1521,6 +1583,7 @@
       </c>
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="n"/>
+      <c r="G51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1541,6 +1604,7 @@
       </c>
       <c r="E52" s="4" t="n"/>
       <c r="F52" s="4" t="n"/>
+      <c r="G52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1561,6 +1625,7 @@
       </c>
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="n"/>
+      <c r="G53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1581,6 +1646,7 @@
       </c>
       <c r="E54" s="4" t="n"/>
       <c r="F54" s="4" t="n"/>
+      <c r="G54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1601,6 +1667,7 @@
       </c>
       <c r="E55" s="4" t="n"/>
       <c r="F55" s="4" t="n"/>
+      <c r="G55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1621,6 +1688,7 @@
       </c>
       <c r="E56" s="4" t="n"/>
       <c r="F56" s="4" t="n"/>
+      <c r="G56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1641,6 +1709,7 @@
       </c>
       <c r="E57" s="4" t="n"/>
       <c r="F57" s="4" t="n"/>
+      <c r="G57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1661,6 +1730,7 @@
       </c>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
+      <c r="G58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1681,6 +1751,7 @@
       </c>
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
+      <c r="G59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1701,6 +1772,7 @@
       </c>
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
+      <c r="G60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1721,6 +1793,7 @@
       </c>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
+      <c r="G61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1741,6 +1814,7 @@
       </c>
       <c r="E62" s="4" t="n"/>
       <c r="F62" s="4" t="n"/>
+      <c r="G62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1761,6 +1835,7 @@
       </c>
       <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="n"/>
+      <c r="G63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1781,6 +1856,7 @@
       </c>
       <c r="E64" s="4" t="n"/>
       <c r="F64" s="4" t="n"/>
+      <c r="G64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1801,6 +1877,7 @@
       </c>
       <c r="E65" s="4" t="n"/>
       <c r="F65" s="4" t="n"/>
+      <c r="G65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1821,6 +1898,7 @@
       </c>
       <c r="E66" s="4" t="n"/>
       <c r="F66" s="4" t="n"/>
+      <c r="G66" s="5" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -1841,6 +1919,7 @@
       </c>
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n"/>
+      <c r="G67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1861,6 +1940,7 @@
       </c>
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
+      <c r="G68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -1881,6 +1961,7 @@
       </c>
       <c r="E69" s="4" t="n"/>
       <c r="F69" s="4" t="n"/>
+      <c r="G69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -1901,6 +1982,7 @@
       </c>
       <c r="E70" s="4" t="n"/>
       <c r="F70" s="4" t="n"/>
+      <c r="G70" s="5" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -1921,6 +2003,7 @@
       </c>
       <c r="E71" s="4" t="n"/>
       <c r="F71" s="4" t="n"/>
+      <c r="G71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -1941,6 +2024,7 @@
       </c>
       <c r="E72" s="4" t="n"/>
       <c r="F72" s="4" t="n"/>
+      <c r="G72" s="5" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -1961,6 +2045,7 @@
       </c>
       <c r="E73" s="4" t="n"/>
       <c r="F73" s="4" t="n"/>
+      <c r="G73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -1981,6 +2066,7 @@
       </c>
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
+      <c r="G74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2001,6 +2087,7 @@
       </c>
       <c r="E75" s="4" t="n"/>
       <c r="F75" s="4" t="n"/>
+      <c r="G75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2021,6 +2108,7 @@
       </c>
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="n"/>
+      <c r="G76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2041,6 +2129,7 @@
       </c>
       <c r="E77" s="4" t="n"/>
       <c r="F77" s="4" t="n"/>
+      <c r="G77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2061,6 +2150,7 @@
       </c>
       <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="n"/>
+      <c r="G78" s="5" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2081,6 +2171,7 @@
       </c>
       <c r="E79" s="4" t="n"/>
       <c r="F79" s="4" t="n"/>
+      <c r="G79" s="5" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2101,6 +2192,7 @@
       </c>
       <c r="E80" s="4" t="n"/>
       <c r="F80" s="4" t="n"/>
+      <c r="G80" s="5" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2121,6 +2213,7 @@
       </c>
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
+      <c r="G81" s="5" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2141,6 +2234,7 @@
       </c>
       <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="n"/>
+      <c r="G82" s="5" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2161,6 +2255,7 @@
       </c>
       <c r="E83" s="4" t="n"/>
       <c r="F83" s="4" t="n"/>
+      <c r="G83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2181,6 +2276,7 @@
       </c>
       <c r="E84" s="4" t="n"/>
       <c r="F84" s="4" t="n"/>
+      <c r="G84" s="5" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2201,6 +2297,7 @@
       </c>
       <c r="E85" s="4" t="n"/>
       <c r="F85" s="4" t="n"/>
+      <c r="G85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2221,6 +2318,7 @@
       </c>
       <c r="E86" s="4" t="n"/>
       <c r="F86" s="4" t="n"/>
+      <c r="G86" s="5" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2241,6 +2339,7 @@
       </c>
       <c r="E87" s="4" t="n"/>
       <c r="F87" s="4" t="n"/>
+      <c r="G87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2261,6 +2360,7 @@
       </c>
       <c r="E88" s="4" t="n"/>
       <c r="F88" s="4" t="n"/>
+      <c r="G88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -2281,6 +2381,7 @@
       </c>
       <c r="E89" s="4" t="n"/>
       <c r="F89" s="4" t="n"/>
+      <c r="G89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2301,6 +2402,7 @@
       </c>
       <c r="E90" s="4" t="n"/>
       <c r="F90" s="4" t="n"/>
+      <c r="G90" s="5" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -2321,6 +2423,7 @@
       </c>
       <c r="E91" s="4" t="n"/>
       <c r="F91" s="4" t="n"/>
+      <c r="G91" s="5" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -2341,6 +2444,7 @@
       </c>
       <c r="E92" s="4" t="n"/>
       <c r="F92" s="4" t="n"/>
+      <c r="G92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2361,6 +2465,7 @@
       </c>
       <c r="E93" s="4" t="n"/>
       <c r="F93" s="4" t="n"/>
+      <c r="G93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -2381,6 +2486,7 @@
       </c>
       <c r="E94" s="4" t="n"/>
       <c r="F94" s="4" t="n"/>
+      <c r="G94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -2401,6 +2507,7 @@
       </c>
       <c r="E95" s="4" t="n"/>
       <c r="F95" s="4" t="n"/>
+      <c r="G95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -2421,6 +2528,7 @@
       </c>
       <c r="E96" s="4" t="n"/>
       <c r="F96" s="4" t="n"/>
+      <c r="G96" s="5" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -2441,6 +2549,7 @@
       </c>
       <c r="E97" s="4" t="n"/>
       <c r="F97" s="4" t="n"/>
+      <c r="G97" s="5" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -2461,6 +2570,7 @@
       </c>
       <c r="E98" s="4" t="n"/>
       <c r="F98" s="4" t="n"/>
+      <c r="G98" s="5" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -2481,6 +2591,7 @@
       </c>
       <c r="E99" s="4" t="n"/>
       <c r="F99" s="4" t="n"/>
+      <c r="G99" s="5" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -2501,6 +2612,7 @@
       </c>
       <c r="E100" s="4" t="n"/>
       <c r="F100" s="4" t="n"/>
+      <c r="G100" s="5" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -2521,6 +2633,7 @@
       </c>
       <c r="E101" s="4" t="n"/>
       <c r="F101" s="4" t="n"/>
+      <c r="G101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -2541,6 +2654,7 @@
       </c>
       <c r="E102" s="4" t="n"/>
       <c r="F102" s="4" t="n"/>
+      <c r="G102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -2561,6 +2675,7 @@
       </c>
       <c r="E103" s="4" t="n"/>
       <c r="F103" s="4" t="n"/>
+      <c r="G103" s="5" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -2581,6 +2696,7 @@
       </c>
       <c r="E104" s="4" t="n"/>
       <c r="F104" s="4" t="n"/>
+      <c r="G104" s="5" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -2601,6 +2717,7 @@
       </c>
       <c r="E105" s="4" t="n"/>
       <c r="F105" s="4" t="n"/>
+      <c r="G105" s="5" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -2621,6 +2738,7 @@
       </c>
       <c r="E106" s="4" t="n"/>
       <c r="F106" s="4" t="n"/>
+      <c r="G106" s="5" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -2641,6 +2759,7 @@
       </c>
       <c r="E107" s="4" t="n"/>
       <c r="F107" s="4" t="n"/>
+      <c r="G107" s="5" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -2661,6 +2780,7 @@
       </c>
       <c r="E108" s="4" t="n"/>
       <c r="F108" s="4" t="n"/>
+      <c r="G108" s="5" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -2681,6 +2801,7 @@
       </c>
       <c r="E109" s="4" t="n"/>
       <c r="F109" s="4" t="n"/>
+      <c r="G109" s="5" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -2701,6 +2822,7 @@
       </c>
       <c r="E110" s="4" t="n"/>
       <c r="F110" s="4" t="n"/>
+      <c r="G110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -2721,6 +2843,7 @@
       </c>
       <c r="E111" s="4" t="n"/>
       <c r="F111" s="4" t="n"/>
+      <c r="G111" s="5" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -2741,6 +2864,7 @@
       </c>
       <c r="E112" s="4" t="n"/>
       <c r="F112" s="4" t="n"/>
+      <c r="G112" s="5" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -2761,6 +2885,7 @@
       </c>
       <c r="E113" s="4" t="n"/>
       <c r="F113" s="4" t="n"/>
+      <c r="G113" s="5" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -2781,6 +2906,7 @@
       </c>
       <c r="E114" s="4" t="n"/>
       <c r="F114" s="4" t="n"/>
+      <c r="G114" s="5" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -2801,6 +2927,7 @@
       </c>
       <c r="E115" s="4" t="n"/>
       <c r="F115" s="4" t="n"/>
+      <c r="G115" s="5" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -2821,6 +2948,7 @@
       </c>
       <c r="E116" s="4" t="n"/>
       <c r="F116" s="4" t="n"/>
+      <c r="G116" s="5" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -2841,6 +2969,7 @@
       </c>
       <c r="E117" s="4" t="n"/>
       <c r="F117" s="4" t="n"/>
+      <c r="G117" s="5" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -2861,6 +2990,7 @@
       </c>
       <c r="E118" s="4" t="n"/>
       <c r="F118" s="4" t="n"/>
+      <c r="G118" s="5" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -2881,6 +3011,7 @@
       </c>
       <c r="E119" s="4" t="n"/>
       <c r="F119" s="4" t="n"/>
+      <c r="G119" s="5" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -2901,6 +3032,7 @@
       </c>
       <c r="E120" s="4" t="n"/>
       <c r="F120" s="4" t="n"/>
+      <c r="G120" s="5" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -2921,6 +3053,7 @@
       </c>
       <c r="E121" s="4" t="n"/>
       <c r="F121" s="4" t="n"/>
+      <c r="G121" s="5" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -2941,6 +3074,7 @@
       </c>
       <c r="E122" s="4" t="n"/>
       <c r="F122" s="4" t="n"/>
+      <c r="G122" s="5" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -2961,6 +3095,7 @@
       </c>
       <c r="E123" s="4" t="n"/>
       <c r="F123" s="4" t="n"/>
+      <c r="G123" s="5" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -2981,6 +3116,7 @@
       </c>
       <c r="E124" s="4" t="n"/>
       <c r="F124" s="4" t="n"/>
+      <c r="G124" s="5" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -3001,6 +3137,7 @@
       </c>
       <c r="E125" s="4" t="n"/>
       <c r="F125" s="4" t="n"/>
+      <c r="G125" s="5" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3021,6 +3158,7 @@
       </c>
       <c r="E126" s="4" t="n"/>
       <c r="F126" s="4" t="n"/>
+      <c r="G126" s="5" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -3041,6 +3179,7 @@
       </c>
       <c r="E127" s="4" t="n"/>
       <c r="F127" s="4" t="n"/>
+      <c r="G127" s="5" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -3061,6 +3200,7 @@
       </c>
       <c r="E128" s="4" t="n"/>
       <c r="F128" s="4" t="n"/>
+      <c r="G128" s="5" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -3081,6 +3221,7 @@
       </c>
       <c r="E129" s="4" t="n"/>
       <c r="F129" s="4" t="n"/>
+      <c r="G129" s="5" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -3101,6 +3242,7 @@
       </c>
       <c r="E130" s="4" t="n"/>
       <c r="F130" s="4" t="n"/>
+      <c r="G130" s="5" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -3121,6 +3263,7 @@
       </c>
       <c r="E131" s="4" t="n"/>
       <c r="F131" s="4" t="n"/>
+      <c r="G131" s="5" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -3141,6 +3284,7 @@
       </c>
       <c r="E132" s="4" t="n"/>
       <c r="F132" s="4" t="n"/>
+      <c r="G132" s="5" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -3161,6 +3305,7 @@
       </c>
       <c r="E133" s="4" t="n"/>
       <c r="F133" s="4" t="n"/>
+      <c r="G133" s="5" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -3181,6 +3326,7 @@
       </c>
       <c r="E134" s="4" t="n"/>
       <c r="F134" s="4" t="n"/>
+      <c r="G134" s="5" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -3201,6 +3347,7 @@
       </c>
       <c r="E135" s="4" t="n"/>
       <c r="F135" s="4" t="n"/>
+      <c r="G135" s="5" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -3221,6 +3368,7 @@
       </c>
       <c r="E136" s="4" t="n"/>
       <c r="F136" s="4" t="n"/>
+      <c r="G136" s="5" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -3241,6 +3389,7 @@
       </c>
       <c r="E137" s="4" t="n"/>
       <c r="F137" s="4" t="n"/>
+      <c r="G137" s="5" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -3261,6 +3410,7 @@
       </c>
       <c r="E138" s="4" t="n"/>
       <c r="F138" s="4" t="n"/>
+      <c r="G138" s="5" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -3281,6 +3431,7 @@
       </c>
       <c r="E139" s="4" t="n"/>
       <c r="F139" s="4" t="n"/>
+      <c r="G139" s="5" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -3301,6 +3452,7 @@
       </c>
       <c r="E140" s="4" t="n"/>
       <c r="F140" s="4" t="n"/>
+      <c r="G140" s="5" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -3321,6 +3473,7 @@
       </c>
       <c r="E141" s="4" t="n"/>
       <c r="F141" s="4" t="n"/>
+      <c r="G141" s="5" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -3341,6 +3494,7 @@
       </c>
       <c r="E142" s="4" t="n"/>
       <c r="F142" s="4" t="n"/>
+      <c r="G142" s="5" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -3361,6 +3515,7 @@
       </c>
       <c r="E143" s="4" t="n"/>
       <c r="F143" s="4" t="n"/>
+      <c r="G143" s="5" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -3381,6 +3536,7 @@
       </c>
       <c r="E144" s="4" t="n"/>
       <c r="F144" s="4" t="n"/>
+      <c r="G144" s="5" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -3401,6 +3557,7 @@
       </c>
       <c r="E145" s="4" t="n"/>
       <c r="F145" s="4" t="n"/>
+      <c r="G145" s="5" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -3421,6 +3578,7 @@
       </c>
       <c r="E146" s="4" t="n"/>
       <c r="F146" s="4" t="n"/>
+      <c r="G146" s="5" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -3441,6 +3599,7 @@
       </c>
       <c r="E147" s="4" t="n"/>
       <c r="F147" s="4" t="n"/>
+      <c r="G147" s="5" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -3461,6 +3620,7 @@
       </c>
       <c r="E148" s="4" t="n"/>
       <c r="F148" s="4" t="n"/>
+      <c r="G148" s="5" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -3481,6 +3641,7 @@
       </c>
       <c r="E149" s="4" t="n"/>
       <c r="F149" s="4" t="n"/>
+      <c r="G149" s="5" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -3501,6 +3662,7 @@
       </c>
       <c r="E150" s="4" t="n"/>
       <c r="F150" s="4" t="n"/>
+      <c r="G150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -3521,6 +3683,7 @@
       </c>
       <c r="E151" s="4" t="n"/>
       <c r="F151" s="4" t="n"/>
+      <c r="G151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -3541,6 +3704,7 @@
       </c>
       <c r="E152" s="4" t="n"/>
       <c r="F152" s="4" t="n"/>
+      <c r="G152" s="5" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -3561,6 +3725,7 @@
       </c>
       <c r="E153" s="4" t="n"/>
       <c r="F153" s="4" t="n"/>
+      <c r="G153" s="5" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -3581,6 +3746,7 @@
       </c>
       <c r="E154" s="4" t="n"/>
       <c r="F154" s="4" t="n"/>
+      <c r="G154" s="5" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -3601,6 +3767,7 @@
       </c>
       <c r="E155" s="4" t="n"/>
       <c r="F155" s="4" t="n"/>
+      <c r="G155" s="5" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -3621,6 +3788,7 @@
       </c>
       <c r="E156" s="4" t="n"/>
       <c r="F156" s="4" t="n"/>
+      <c r="G156" s="5" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -3641,6 +3809,7 @@
       </c>
       <c r="E157" s="4" t="n"/>
       <c r="F157" s="4" t="n"/>
+      <c r="G157" s="5" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -3661,6 +3830,7 @@
       </c>
       <c r="E158" s="4" t="n"/>
       <c r="F158" s="4" t="n"/>
+      <c r="G158" s="5" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -3681,6 +3851,7 @@
       </c>
       <c r="E159" s="4" t="n"/>
       <c r="F159" s="4" t="n"/>
+      <c r="G159" s="5" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -3701,6 +3872,7 @@
       </c>
       <c r="E160" s="4" t="n"/>
       <c r="F160" s="4" t="n"/>
+      <c r="G160" s="5" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -3721,6 +3893,7 @@
       </c>
       <c r="E161" s="4" t="n"/>
       <c r="F161" s="4" t="n"/>
+      <c r="G161" s="5" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -3741,6 +3914,7 @@
       </c>
       <c r="E162" s="4" t="n"/>
       <c r="F162" s="4" t="n"/>
+      <c r="G162" s="5" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -3761,6 +3935,7 @@
       </c>
       <c r="E163" s="4" t="n"/>
       <c r="F163" s="4" t="n"/>
+      <c r="G163" s="5" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -3781,6 +3956,7 @@
       </c>
       <c r="E164" s="4" t="n"/>
       <c r="F164" s="4" t="n"/>
+      <c r="G164" s="5" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -3801,6 +3977,7 @@
       </c>
       <c r="E165" s="4" t="n"/>
       <c r="F165" s="4" t="n"/>
+      <c r="G165" s="5" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -3821,6 +3998,7 @@
       </c>
       <c r="E166" s="4" t="n"/>
       <c r="F166" s="4" t="n"/>
+      <c r="G166" s="5" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -3841,6 +4019,7 @@
       </c>
       <c r="E167" s="4" t="n"/>
       <c r="F167" s="4" t="n"/>
+      <c r="G167" s="5" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -3861,6 +4040,7 @@
       </c>
       <c r="E168" s="4" t="n"/>
       <c r="F168" s="4" t="n"/>
+      <c r="G168" s="5" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -3881,6 +4061,7 @@
       </c>
       <c r="E169" s="4" t="n"/>
       <c r="F169" s="4" t="n"/>
+      <c r="G169" s="5" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -3901,6 +4082,7 @@
       </c>
       <c r="E170" s="4" t="n"/>
       <c r="F170" s="4" t="n"/>
+      <c r="G170" s="5" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -3921,6 +4103,7 @@
       </c>
       <c r="E171" s="4" t="n"/>
       <c r="F171" s="4" t="n"/>
+      <c r="G171" s="5" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -3941,6 +4124,7 @@
       </c>
       <c r="E172" s="4" t="n"/>
       <c r="F172" s="4" t="n"/>
+      <c r="G172" s="5" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -3961,6 +4145,7 @@
       </c>
       <c r="E173" s="4" t="n"/>
       <c r="F173" s="4" t="n"/>
+      <c r="G173" s="5" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -3981,6 +4166,7 @@
       </c>
       <c r="E174" s="4" t="n"/>
       <c r="F174" s="4" t="n"/>
+      <c r="G174" s="5" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -4001,6 +4187,7 @@
       </c>
       <c r="E175" s="4" t="n"/>
       <c r="F175" s="4" t="n"/>
+      <c r="G175" s="5" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -4021,6 +4208,7 @@
       </c>
       <c r="E176" s="4" t="n"/>
       <c r="F176" s="4" t="n"/>
+      <c r="G176" s="5" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -4041,6 +4229,7 @@
       </c>
       <c r="E177" s="4" t="n"/>
       <c r="F177" s="4" t="n"/>
+      <c r="G177" s="5" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -4061,6 +4250,7 @@
       </c>
       <c r="E178" s="4" t="n"/>
       <c r="F178" s="4" t="n"/>
+      <c r="G178" s="5" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -4081,6 +4271,7 @@
       </c>
       <c r="E179" s="4" t="n"/>
       <c r="F179" s="4" t="n"/>
+      <c r="G179" s="5" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -4101,6 +4292,7 @@
       </c>
       <c r="E180" s="4" t="n"/>
       <c r="F180" s="4" t="n"/>
+      <c r="G180" s="5" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -4121,6 +4313,7 @@
       </c>
       <c r="E181" s="4" t="n"/>
       <c r="F181" s="4" t="n"/>
+      <c r="G181" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4133,140 +4326,192 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>COMO PREENCHER O TARGET FINANCEIRO</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr"/>
+      <c r="A2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1. Aba 'Targets' tem uma linha por PRODUTO × MÊS (2026 completo já estruturado).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>2. Preencha as colunas amarelas: TARGET_BRL (meta em reais) e TARGET_UNID (meta em unidades).</t>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>2. Preencha as colunas amarelas/verdes conforme as métricas que você usa:</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>3. NÃO altere os nomes das colunas (FRANQUIA, PRODUTO, ANO, MES_NUM, TARGET_BRL, TARGET_UNID).</t>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - TARGET_BRL (amarela): meta em Reais</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr"/>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - TARGET_UNID (amarela): meta em Unidades</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   - TARGET_USD (verde): meta em Dólares — NOVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>3. NÃO altere os nomes das colunas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
           <t>IMPORTANTE - match de produtos:</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>- O nome em PRODUTO deve bater EXATAMENTE com o que aparece no dashboard (após De-Para).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>- Os produtos aqui são EXEMPLOS. Ajuste/adicione/remova conforme sua base real.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>O QUE O DASHBOARD CALCULA AUTOMATICAMENTE:</t>
+          <t>- O nome em PRODUTO deve bater EXATAMENTE com o que aparece no dashboard (após De-Para).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>- Atingimento do MÊS atual (Real vs Target do mês)</t>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>- Os produtos aqui são EXEMPLOS. Ajuste/adicione/remova conforme sua base real.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>- Atingimento YTD (Real acumulado vs Target acumulado Jan→mês)</t>
-        </is>
-      </c>
+      <c r="A13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>- Atingimento ANO (projeção anualizada vs Target do ano)</t>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>VOCÊ PODE PREENCHER SÓ AS MÉTRICAS QUE PRECISAR:</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>- Atingimento POR PRODUTO (tabela detalhada - NOVO)</t>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>- Só TARGET_BRL → atingimento em Reais funciona</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr"/>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>- Só TARGET_USD → atingimento em USD funciona</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
+          <t>- Pode mixar: preencher BRL para alguns produtos e USD para outros</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>- Se uma métrica não tem target preenchido, o dashboard mostra aviso claro</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>O QUE O DASHBOARD CALCULA AUTOMATICAMENTE:</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>- Atingimento do MÊS atual (Real vs Target do mês)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>- Atingimento YTD (Real acumulado vs Target acumulado Jan→mês)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>- Atingimento ANO (projeção anualizada vs Target do ano)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>- Atingimento POR PRODUTO (tabela detalhada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
           <t>DICAS:</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>- Deixe em branco (ou 0) os meses/produtos sem meta - eles aparecem como 'sem target'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>- Pode adicionar outros anos (2025, 2027) - basta novas linhas com o ANO correto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>- Deixe em branco (ou 0) os meses/produtos sem meta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>- Pode adicionar outros anos (2025, 2027) - basta novas linhas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>- Target é a nível EMPRESA (não por cliente). Com cliente filtrado, mostra N/A.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>- USD não tem target (só BRL e Unidades).</t>
         </is>
       </c>
     </row>
